--- a/ScTypeDB_full.xlsx
+++ b/ScTypeDB_full.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jdg67/Desktop/Xenium/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jdg67/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7283392-6396-D54F-94B5-2C165A638415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F87014-3FFD-9A42-90FE-2B3D04F2D11E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="333">
   <si>
     <t>tissueType</t>
   </si>
@@ -943,13 +943,109 @@
   </si>
   <si>
     <t>Fap,Fzd1,Fzd2,Fzd4,Fabp4,Adipoq,Lpl,Postn,Mmp13,Crabp1,Cpxm1,col3a1,Bmp2,Cavin2,Ackr3,Marco,Anxa2,Nts,Htra3,Ccdc80,Cfh,Eng,Gpihbp1,Ctla2a,Tnfaip6,Cnn1,Dpt,Lum,Retn,Mylk,Plvap,Wif1,Col8a1,Otor,Tmem100,Hpgd,Aspn,Mustn1,Mfap4,Sod3,Vwf,Clec14a,Gng11,Nbl1,Bgn,Cav1,Aqp7,Serpina3n,Tie1,AU021092,Tcf15,Angpt2,Mamdc2</t>
+  </si>
+  <si>
+    <t>Lung</t>
+  </si>
+  <si>
+    <t>Airway epithelial cells</t>
+  </si>
+  <si>
+    <t>ADH7,AQP1,CDH1,SEC14L3</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>Airway goblet cells</t>
+  </si>
+  <si>
+    <t>AGR2,AQP5,CEACAM1,DMBT1,DUSP4,FXYD3,GALNT5,GALNT6,GGH,GOLPH3,GP2,IL19,LIPF,LTF,LYNX1,MSLN,MUC16,MUC4,MUC5B,NOS2,PIGR,QSOX1,SCGB3A1,SEC23B,SPDEF,TFF2</t>
+  </si>
+  <si>
+    <t>Mesothelial cells</t>
+  </si>
+  <si>
+    <t>C2,CALB2,CD44,CDH1,DES,EFEMP1,EPCAM,GSTA3,KRT5,KRT7,KRT72,LGALS7,LRRN4,ME1,ME2,MSLN,MUC16,OSR1,RSPO1,THBD,UPK3B,WT1</t>
+  </si>
+  <si>
+    <t>Fibroblasts</t>
+  </si>
+  <si>
+    <t>COL3A1,COL5A2,DPT,FN1,GSN,LRP1,PDGFRA,TCF21</t>
+  </si>
+  <si>
+    <t>Basal cells (Airway progenitor cells)</t>
+  </si>
+  <si>
+    <t>ABI3BP,AQP3,DAPL1,GSTM2,HPGD,ICAM1,KRT14,KRT15,KRT5,PHLDA3,RPS18,SDC1</t>
+  </si>
+  <si>
+    <t>Alveolar macrophages</t>
+  </si>
+  <si>
+    <t>ABCG1,CCL3,CD36,CLEC7A,CSF2RB,CXCL2,G0S2,GAL,GDA,GNGT2,GPNMB,IL18,IL1B,ITGAX,KLHDC4,MARCO,MCEMP1,MPP1,MRC1,OLR1,PLET1,S100A4,TLR2,TNFAIP2,TRIM25</t>
+  </si>
+  <si>
+    <t>Ciliated cells</t>
+  </si>
+  <si>
+    <t>APPL2,ATP5MD,CCDC153,CCDC17,CCDC181,CCDC39,CYP2S1,FAM161A,FOXJ1,LRRC23,ODF3B,SCGB1A1,SEC14L3,SNTN,STK11,TMEM212,TSPAN19,TUBB4B</t>
+  </si>
+  <si>
+    <t>Clara cells</t>
+  </si>
+  <si>
+    <t>AHR,ALDH1A1,BPIFA1,CTSE,CYP2E1,CYP4B1,ERN1,FOXM1,LEPR,MUC1,MUC4,MUC5B,RAB3D,SCGB1A1,SCGB3A1,SCGB3A2,SFTPA1,SFTPC,SFTPD,SYT2</t>
+  </si>
+  <si>
+    <t>Immune system cells</t>
+  </si>
+  <si>
+    <t>ADGRE1,ARG1,BIRC5,CCL17,CCL18,CD14,CD163,CD19,CD22,CD3D,CD3E,CD3G,CD4,CD44,CD5,CD68,CD74,CD80,CD83,CD86,CD8A,CD8B,CDCA3,CDK1,CEBPE,CR2,CSF1R,EAF2,FCER2,FCGR3A,FLT3,GIMAP3P,HLA-DRA,HMMR,IGHM,IL2RA,ITGAE,ITGAM,ITGAX,LAX1,MS4A14,MZB1,NRP1,NUSAP1,PAX5,PRG2,PTPRC,SLPI,THBD,TNFRSF17,TRBC1,XCR1</t>
+  </si>
+  <si>
+    <t>Endothelial cell</t>
+  </si>
+  <si>
+    <t>CD34,EGFL7,EMCN,ESAM,FLT1,KDR,MCAM,PECAM1,RAMP2,TEK,VWF</t>
+  </si>
+  <si>
+    <t>Epithelial cells</t>
+  </si>
+  <si>
+    <t>ANPEP,EPCAM,IL10,IL6R</t>
+  </si>
+  <si>
+    <t>Ionocytes</t>
+  </si>
+  <si>
+    <t>CFTR,CLCNKB,FOXI1,KCNMA1,SCGB1A1,SLC12A2,TFCP2L1</t>
+  </si>
+  <si>
+    <t>Pulmonary alveolar type I cells</t>
+  </si>
+  <si>
+    <t>AGER,AKAP5,AQP3,AQP5,CCN2,CLDN18,CLIC5,COL4A3,COL4A4,CRLF1,CYP4B1,EGFL6,EMP2,FSTL3,GPRC5A,HOPX,ICAM1,IGFBP6,KRT7,MEX3B,MMP11,P2RX7,PDPN,PXDC1,RTKN2,SCNN1A,SCNN1B,SCNN1G,SEC14L3,SEMA3B,SEMA3E,SMARCA1,VEGFA</t>
+  </si>
+  <si>
+    <t>Pulmonary alveolar type II cells</t>
+  </si>
+  <si>
+    <t>ABCA3,ADGRF5,AGER,CD36,CD3G,CEBPA,CLDN18,CRLF1,CTNND1,CXCL2,CXCR2,DDX3Y,EGFL6,ETV5,GRK2,IL1B,INMT,IRX1,LAMP3,LPCAT1,LRG1,MUC1,NAPSA,NKX2-1,NRN1,PGC,PIGR,PPBP,PPP1R14C,RUNX3,S100G,SDC1,SFTA2,SFTPA1,SFTPB,SFTPC,SFTPD,SLC34A2,SOAT1</t>
+  </si>
+  <si>
+    <t>Secretory cell</t>
+  </si>
+  <si>
+    <t>MUC5B,PIGR,SCGB1A1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -991,6 +1087,12 @@
       <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF858796"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1012,7 +1114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1047,6 +1149,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1442,7 +1545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E146"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
@@ -3022,7 +3125,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>293</v>
       </c>
@@ -3033,7 +3136,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>293</v>
       </c>
@@ -3044,7 +3147,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>293</v>
       </c>
@@ -3055,15 +3158,222 @@
         <v>300</v>
       </c>
     </row>
+    <row r="132" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A132" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B132" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="D132" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A133" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B133" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D133" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A134" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B134" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A135" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B135" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="C135" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A136" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B136" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A137" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B137" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A138" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B138" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="D138" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A139" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B139" s="12" t="s">
+        <v>317</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="D139" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A140" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B140" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C140" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="D140" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A141" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B141" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="D141" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A142" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B142" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="C142" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="D142" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A143" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B143" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="C143" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="D143" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A144" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B144" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="C144" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="D144" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A145" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B145" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="D145" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="20" x14ac:dyDescent="0.2">
+      <c r="A146" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="B146" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="C146" s="12" t="s">
+        <v>332</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="B1:B42 B44:B76 B103:B1048576">
+  <conditionalFormatting sqref="B1:B42 B44:B76 B103:B131 B147:B1048576">
     <cfRule type="duplicateValues" dxfId="7" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B76 B103:B1048576">
+  <conditionalFormatting sqref="B1:B76 B103:B131 B147:B1048576">
     <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
+  <conditionalFormatting sqref="B1:B131 B147:B1048576">
     <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B77:B81">
@@ -3074,7 +3384,7 @@
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
     <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B103:B1048576 B67:B76 B1:B42 B44:B65">
+  <conditionalFormatting sqref="B103:B131 B67:B76 B1:B42 B44:B65 B147:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
